--- a/consent_forms/026_child_medical_consent_form--consent_forms.xlsx
+++ b/consent_forms/026_child_medical_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -889,8 +889,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -918,12 +918,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'routine_check-ups_and_exams',_'value':_'exams'}</t>
+          <t>routine_check-ups_and_exams</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Routine Check-ups and Exams', 'value': 'exams'}</t>
+          <t>Routine Check-ups and Exams</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'required_vaccinations',_'value':_'vaccines'}</t>
+          <t>required_vaccinations</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Required Vaccinations', 'value': 'vaccines'}</t>
+          <t>Required Vaccinations</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'diagnostic_lab_tests',_'value':_'labs'}</t>
+          <t>diagnostic_lab_tests</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Diagnostic Lab Tests', 'value': 'labs'}</t>
+          <t>Diagnostic Lab Tests</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'emergency_medical_care',_'value':_'emergency'}</t>
+          <t>emergency_medical_care</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Emergency Medical Care', 'value': 'emergency'}</t>
+          <t>Emergency Medical Care</t>
         </is>
       </c>
     </row>
